--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -2,32 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -53,12 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -421,54 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="16.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CPF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Telefone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Endereço</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Data Cadastro</t>
         </is>
@@ -480,32 +464,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>Kaua</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>12345678910</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>K@k</t>
+          <t>kaua@gmail.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>4112345678</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>Rua Tal, 123</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>
@@ -515,173 +499,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>jeferson luiz veiga junior</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>14338958979</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>k@k</t>
+          <t>jefersonluizveiga888@gmail.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>41988885789</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>k</t>
-        </is>
-      </c>
+          <t>rua nova aurora 278</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>k@k</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>k@k</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kauã</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>12345678910</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>kaua@gmail.com</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4112345678</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rua Tal, 123</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>João</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>98765432110</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>joao@gmail.com</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4198765432</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rual Tal 2, 321</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>

--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,10 +522,45 @@
           <t>rua nova aurora 278</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>98765432110</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>joao@gmail.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41987654321</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rua Tal, 321</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>

--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -337,7 +337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20.21" customWidth="1" style="1" min="2" max="2"/>
@@ -928,38 +928,146 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>mayke</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>3427761123</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>mayke@gmail.com</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>888663882</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>rua pioneiros</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
+      <c r="G17" s="1" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>92345492734</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>jose@gmail.com</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>41937529547</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Rual Jose, 543</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>92345492734</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>jose@gmail.com</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>41937529547</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Rual Jose, 543</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>92345492734</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jose@gmail.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>41937529547</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rual Jose, 543</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>

--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -4,26 +4,41 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,16 +58,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -125,41 +157,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -167,369 +199,346 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="9.140000000000001" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.18" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.52" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12.18" customWidth="1" style="1" min="5" max="5"/>
+    <col width="11.1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="11.53" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12.72" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>CPF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Telefone</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Endereço</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Data Cadastro</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="15" customHeight="1" s="2">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Kaua</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>12345678910</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>kaua@gmail.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>4112345678</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Rua Tal, 123</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="15" customHeight="1" s="2">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Kauan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>10123455678</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>KJNK@KSJDNV</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>skancJNK</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>KAJNV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="2">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mayke 28</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>12948293857</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>mayke@gmail.com</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>36463463463</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>aijfijanijna</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1845284583</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>joa@gmai.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8374658347</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>jnskdjnksjn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>joao 28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -2,43 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,33 +42,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -157,41 +124,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -199,300 +166,408 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9.140000000000001" customWidth="1" style="1" min="2" max="2"/>
-    <col width="12.18" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.52" customWidth="1" style="1" min="4" max="4"/>
-    <col width="12.18" customWidth="1" style="1" min="5" max="5"/>
-    <col width="11.1" customWidth="1" style="1" min="6" max="6"/>
-    <col width="11.53" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12.72" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="21" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="23.44140625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.44140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="2">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CPF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Telefone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Endereço</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Data Cadastro</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="2">
-      <c r="A2" s="1" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Kaua</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>12345678910</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>kaua@gmail.com</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>4112345678</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Rua Tal, 123</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="2">
-      <c r="A3" s="1" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Kauan</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>10123455678</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>KJNK@KSJDNV</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>skancJNK</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>KAJNV</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="2">
-      <c r="A4" s="1" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Mayke 28</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>12948293857</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>mayke@gmail.com</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>36463463463</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>aijfijanijna</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
         </is>
       </c>
     </row>
@@ -502,43 +577,216 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>José Antônio dos Reis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1845284583</t>
+          <t>087.280.297-39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>joa@gmai.com</t>
+          <t>apoio.klesis828320@gmail.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8374658347</t>
+          <t>41985147636</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jnskdjnksjn</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>joao 28</t>
+          <t>Rua das Naçõs unidas - 871</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis9999</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis 14-04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>José Antônio dos Reis 05/06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>087.280.297-39</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>apoio.klesis@gmail.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>41985147636</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rua das Naçõs unidas - 871</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 05/05</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>